--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104619_W18.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104619_W18.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5848</v>
+        <v>4.2578</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8409</v>
+        <v>3.3551</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7439</v>
+        <v>0.9028</v>
       </c>
       <c r="G2" t="n">
-        <v>1.068</v>
+        <v>1.0285</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.3976</v>
+        <v>-1.4368</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4656</v>
+        <v>2.4653</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5651</v>
+        <v>1.5016</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0742</v>
+        <v>-0.1291</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6392</v>
+        <v>1.6308</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4971</v>
+        <v>-0.4731</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.3234</v>
+        <v>-1.3077</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8934</v>
+        <v>-0.1789</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.868</v>
+        <v>-0.2769</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0254</v>
+        <v>0.098</v>
       </c>
       <c r="V2" t="n">
-        <v>2.9566</v>
+        <v>2.9529</v>
       </c>
       <c r="W2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1542</v>
+        <v>3.745</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0957</v>
+        <v>3.4443</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0585</v>
+        <v>0.3007</v>
       </c>
       <c r="G3" t="n">
-        <v>2.77</v>
+        <v>2.7772</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2714</v>
+        <v>-0.2646</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0414</v>
+        <v>3.0418</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1985</v>
+        <v>3.1913</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1385</v>
+        <v>0.1379</v>
       </c>
       <c r="L3" t="n">
-        <v>3.06</v>
+        <v>3.0534</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4285</v>
+        <v>-0.4141</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4286</v>
+        <v>0.1451</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1028</v>
+        <v>0.253</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3257</v>
+        <v>-0.1078</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1962</v>
+        <v>2.2411</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4938</v>
+        <v>2.6983</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2976</v>
+        <v>-0.4572</v>
       </c>
       <c r="G4" t="n">
-        <v>0.197</v>
+        <v>0.1972</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5468</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7437</v>
+        <v>0.7511</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9609</v>
+        <v>0.9428</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8863</v>
+        <v>0.8683</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7639</v>
+        <v>-0.7457</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.433</v>
+        <v>-1.4223</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6152</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9739</v>
+        <v>-0.7389</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3587</v>
+        <v>0.1699</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W4" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. GUERRA</t>
+          <t>W. VAN BECK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7768</v>
+        <v>1.6381</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2782</v>
+        <v>0.1456</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4986</v>
+        <v>1.4925</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3011</v>
+        <v>1.9389</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4934</v>
+        <v>-1.3957</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8077</v>
+        <v>3.3347</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7783</v>
+        <v>1.565</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0693</v>
+        <v>-1.5103</v>
       </c>
       <c r="L5" t="n">
-        <v>0.709</v>
+        <v>3.0753</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5228</v>
+        <v>0.374</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4241</v>
+        <v>0.1146</v>
       </c>
       <c r="O5" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.2593</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4738</v>
+        <v>-0.0732</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3126</v>
+        <v>-0.2812</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1612</v>
+        <v>0.208</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W. VAN BECK</t>
+          <t>B. FITIPALDO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3167</v>
+        <v>1.4054</v>
       </c>
       <c r="E6" t="n">
-        <v>0.055</v>
+        <v>1.059</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2616</v>
+        <v>0.3464</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9539</v>
+        <v>-0.9584</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.3939</v>
+        <v>-2.0395</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3478</v>
+        <v>1.0812</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5884</v>
+        <v>0.316</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.5034</v>
+        <v>-0.8898</v>
       </c>
       <c r="L6" t="n">
-        <v>3.0919</v>
+        <v>1.2058</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3655</v>
+        <v>-1.2744</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1096</v>
+        <v>-1.1497</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2559</v>
+        <v>-0.1246</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4104</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3992</v>
+        <v>-0.2978</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0112</v>
+        <v>-0.2702</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.0212</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. FITIPALDO</t>
+          <t>F. GUERRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.7446</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3873</v>
+        <v>0.3252</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2179</v>
+        <v>0.4193</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9587</v>
+        <v>1.3083</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0462</v>
+        <v>0.4994</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0875</v>
+        <v>0.8089</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3433</v>
+        <v>0.7764</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.88</v>
+        <v>0.0689</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2233</v>
+        <v>0.7075</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.302</v>
+        <v>0.5319</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1662</v>
+        <v>0.4305</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1359</v>
+        <v>0.1014</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.368</v>
+        <v>0.4378</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0071</v>
+        <v>0.3714</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3608</v>
+        <v>0.0664</v>
       </c>
       <c r="V7" t="n">
-        <v>2.0246</v>
+        <v>-0.7739</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1853</v>
+        <v>0.3155</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>H. ALDERETE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.269</v>
+        <v>-1.1925</v>
       </c>
       <c r="E8" t="n">
-        <v>2.211</v>
+        <v>-0.1968</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.48</v>
+        <v>-0.9957</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5972</v>
+        <v>0.0689</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1947</v>
+        <v>0.2269</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4025</v>
+        <v>-0.1579</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6685</v>
+        <v>-0.2036</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1487</v>
+        <v>0.5861</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5197000000000001</v>
+        <v>-0.7896</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0712</v>
+        <v>0.2725</v>
       </c>
       <c r="N8" t="n">
-        <v>0.046</v>
+        <v>-0.3592</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1172</v>
+        <v>0.6317</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4629</v>
+        <v>-0.0825</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5425</v>
+        <v>0.0068</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0796</v>
+        <v>-0.0893</v>
       </c>
       <c r="V8" t="n">
-        <v>-4.917</v>
+        <v>-1.6342</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.917</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>T. ABROMAITIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2741</v>
+        <v>-1.5123</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6824</v>
+        <v>0.1322</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.9565</v>
+        <v>-1.6445</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.2781</v>
+        <v>-2.0127</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2047</v>
+        <v>-1.399</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.0734</v>
+        <v>-0.6138</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8155</v>
+        <v>-0.2225</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3943</v>
+        <v>-0.5795</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.2098</v>
+        <v>0.357</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4626</v>
+        <v>-1.7902</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.599</v>
+        <v>-0.8194</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8636</v>
+        <v>-0.9708</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0967</v>
+        <v>-0.0035</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3126</v>
+        <v>0.1969</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.216</v>
+        <v>-0.2005</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1853</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1853</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. ABROMAITIS</t>
+          <t>R. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.362</v>
+        <v>-1.6451</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0358</v>
+        <v>-1.908</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3978</v>
+        <v>0.2629</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0172</v>
+        <v>-1.383</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4041</v>
+        <v>-1.5858</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6131</v>
+        <v>0.2028</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2006</v>
+        <v>-0.1795</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5683</v>
+        <v>-0.1346</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3678</v>
+        <v>-0.0449</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8166</v>
+        <v>-1.2034</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8357</v>
+        <v>-1.4511</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9808</v>
+        <v>0.2477</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5878</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>0.16</v>
+        <v>-0.6491</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0756</v>
+        <v>-0.5903</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0844</v>
+        <v>-0.0589</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>0.387</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. GIEDRAITIS</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5628</v>
+        <v>-1.9757</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8923</v>
+        <v>1.3767</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3295</v>
+        <v>-3.3524</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3958</v>
+        <v>0.5986</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5931</v>
+        <v>0.198</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1973</v>
+        <v>0.4006</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1683</v>
+        <v>0.6548</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1283</v>
+        <v>0.1411</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.04</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2275</v>
+        <v>-0.0562</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4648</v>
+        <v>0.0568</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2373</v>
+        <v>-0.113</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.5934</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5526</v>
+        <v>0.7349</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5898</v>
+        <v>0.7219</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0372</v>
+        <v>0.013</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3856</v>
+        <v>-4.9026</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3856</v>
+        <v>-4.9026</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H. ALDERETE</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6463</v>
+        <v>-2.1827</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5454</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1009</v>
+        <v>-3.1218</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0693</v>
+        <v>-3.2953</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2265</v>
+        <v>-0.2176</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1573</v>
+        <v>-3.0777</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1976</v>
+        <v>-1.8482</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5888</v>
+        <v>0.3717</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7864</v>
+        <v>-2.22</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2669</v>
+        <v>-1.4471</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3622</v>
+        <v>-0.5893</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6291</v>
+        <v>-0.8578</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5302</v>
+        <v>0.202</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3478</v>
+        <v>0.6083</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1824</v>
+        <v>-0.4063</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.639</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.519799999999999</v>
+        <v>5.523700000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>11.6424</v>
+        <v>11.3706</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.122800000000001</v>
+        <v>-5.847</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3067000000000005</v>
+        <v>0.2681999999999993</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.943199999999999</v>
+        <v>-7.968599999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>8.249700000000001</v>
+        <v>8.237</v>
       </c>
       <c r="J13" t="n">
-        <v>6.721</v>
+        <v>6.4941</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.9283000000000001</v>
+        <v>-1.0693</v>
       </c>
       <c r="L13" t="n">
-        <v>7.649300000000002</v>
+        <v>7.5634</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.4142</v>
+        <v>-6.2258</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.0145</v>
+        <v>-6.8993</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6003000000000001</v>
+        <v>0.6734000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>7.9392</v>
+        <v>7.9672</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.671</v>
+        <v>-5.691000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>13.6099</v>
+        <v>13.6579</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6049999999999999</v>
+        <v>-0.6045</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0452999999999999</v>
+        <v>-0.02680000000000027</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5595999999999999</v>
+        <v>-0.5777</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1211</v>
+        <v>-2.1074</v>
       </c>
       <c r="W13" t="n">
-        <v>10.6375</v>
+        <v>10.594</v>
       </c>
       <c r="X13" t="n">
-        <v>-12.7587</v>
+        <v>-12.7014</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.0171</v>
+        <v>5.7415</v>
       </c>
       <c r="E14" t="n">
-        <v>7.6827</v>
+        <v>6.9304</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6656</v>
+        <v>-1.1889</v>
       </c>
       <c r="G14" t="n">
-        <v>5.8989</v>
+        <v>5.8913</v>
       </c>
       <c r="H14" t="n">
-        <v>6.4532</v>
+        <v>6.4345</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5543</v>
+        <v>-0.5432</v>
       </c>
       <c r="J14" t="n">
-        <v>6.5986</v>
+        <v>6.5615</v>
       </c>
       <c r="K14" t="n">
-        <v>6.4867</v>
+        <v>6.4498</v>
       </c>
       <c r="L14" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6998</v>
+        <v>-0.6703</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0335</v>
+        <v>-0.0154</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5719</v>
+        <v>0.3055</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9648</v>
+        <v>0.2598</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3929</v>
+        <v>0.0457</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2215</v>
+        <v>1.4308</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8413</v>
+        <v>0.5273</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3802</v>
+        <v>0.9035</v>
       </c>
       <c r="G15" t="n">
-        <v>0.12</v>
+        <v>0.1298</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5945</v>
+        <v>0.5972</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4744</v>
+        <v>-0.4674</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0537</v>
+        <v>-0.0602</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1283</v>
+        <v>-0.1346</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1737</v>
+        <v>0.19</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7228</v>
+        <v>0.7319</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6647</v>
+        <v>0.8732</v>
       </c>
       <c r="T15" t="n">
-        <v>1.978</v>
+        <v>0.6848</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3133</v>
+        <v>0.1884</v>
       </c>
       <c r="V15" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3612</v>
+        <v>0.7679</v>
       </c>
       <c r="E16" t="n">
-        <v>0.09950000000000001</v>
+        <v>2.5041</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2616</v>
+        <v>-1.7362</v>
       </c>
       <c r="G16" t="n">
-        <v>0.308</v>
+        <v>-0.7941</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6651</v>
+        <v>-0.4975</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3572</v>
+        <v>-0.2966</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6461</v>
+        <v>-0.3515</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5715</v>
+        <v>0.1929</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0746</v>
+        <v>-0.5443</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3381</v>
+        <v>-0.4426</v>
       </c>
       <c r="N16" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.6904</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4318</v>
+        <v>0.2477</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9073</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1322</v>
+        <v>0.1163</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2782</v>
+        <v>-0.0863</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1461</v>
+        <v>0.2025</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>3.0392</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>5.2182</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2462</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1725</v>
+        <v>0.2066</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0737</v>
+        <v>0.4925</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0218</v>
+        <v>0.3146</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7602</v>
+        <v>0.669</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7383999999999999</v>
+        <v>-0.3544</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7374</v>
+        <v>0.6433</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3378</v>
+        <v>0.5688</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3997</v>
+        <v>0.0745</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7157</v>
+        <v>-0.3287</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4224</v>
+        <v>0.1002</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1381</v>
+        <v>-0.4289</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.9488</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.6293</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3982</v>
+        <v>0.2056</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1966</v>
+        <v>-0.1604</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2016</v>
+        <v>0.3659</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2249</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8678</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1995</v>
+        <v>0.1049</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2199</v>
+        <v>0.45</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0204</v>
+        <v>-0.3452</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3871</v>
+        <v>0.3989</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.13</v>
+        <v>-0.1211</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5171</v>
+        <v>0.52</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7729</v>
+        <v>0.7709</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1385</v>
+        <v>0.1379</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3858</v>
+        <v>-0.372</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5175</v>
+        <v>0.4101</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4869</v>
+        <v>-0.251</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0044</v>
+        <v>0.6611</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.188</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9628</v>
+        <v>0.3603</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1508</v>
+        <v>-0.2952</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8028</v>
+        <v>2.0212</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5096000000000001</v>
+        <v>2.771</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2932</v>
+        <v>-0.7498</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3299</v>
+        <v>2.7059</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2007</v>
+        <v>2.327</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5306</v>
+        <v>0.3789</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4729</v>
+        <v>-0.6847</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7103</v>
+        <v>0.444</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2373</v>
+        <v>-1.1287</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5878</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-3.6421</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8505</v>
+        <v>1.2324</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6775</v>
+        <v>0.4363</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.173</v>
+        <v>0.7961</v>
       </c>
       <c r="V19" t="n">
-        <v>3.0531</v>
+        <v>-0.2292</v>
       </c>
       <c r="W19" t="n">
-        <v>5.2385</v>
+        <v>0.8603</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6627</v>
+        <v>-0.216</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2936</v>
+        <v>-0.6354</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3691</v>
+        <v>0.4194</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9265</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3476</v>
+        <v>-1.3552</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4211</v>
+        <v>0.4122</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7485</v>
+        <v>-1.7939</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.1482</v>
+        <v>-2.1728</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3997</v>
+        <v>0.3789</v>
       </c>
       <c r="M20" t="n">
-        <v>0.822</v>
+        <v>0.8509</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8006</v>
+        <v>0.8176</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4166</v>
+        <v>0.0441</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7984</v>
+        <v>-0.0887</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6182</v>
+        <v>0.1328</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.692</v>
+        <v>-1.801</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7737000000000001</v>
+        <v>0.3917</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9183</v>
+        <v>-2.1927</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1827</v>
+        <v>-0.2819</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0403</v>
+        <v>-0.0033</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.223</v>
+        <v>-0.2786</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6078</v>
+        <v>0.4336</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6825</v>
+        <v>0.0689</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0746</v>
+        <v>0.3647</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5749</v>
+        <v>-0.7155</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7228</v>
+        <v>-0.0722</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.2976</v>
+        <v>-0.6433</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2373</v>
+        <v>-0.4297</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0344</v>
+        <v>-0.0419</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2029</v>
+        <v>-0.3878</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1386</v>
+        <v>-2.3834</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1615</v>
+        <v>-1.6087</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3001</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2874</v>
+        <v>-2.1706</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0102</v>
+        <v>0.0457</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2772</v>
+        <v>-2.2162</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4397</v>
+        <v>-0.6117</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0693</v>
+        <v>-0.6862</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3705</v>
+        <v>0.0745</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7272</v>
+        <v>-1.5588</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0795</v>
+        <v>0.7319</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-2.2907</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7585</v>
+        <v>0.54</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2782</v>
+        <v>0.2111</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4803</v>
+        <v>0.3289</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0728</v>
+        <v>-2.6301</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2234</v>
+        <v>-1.1166</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8494</v>
+        <v>-1.5134</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7004</v>
+        <v>-1.6928</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4054</v>
+        <v>0.4104</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.1057</v>
+        <v>-2.1032</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6669</v>
+        <v>-0.6774</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8312</v>
+        <v>0.8274</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0335</v>
+        <v>-1.0154</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.3031</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5565</v>
+        <v>-0.4392</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1769</v>
+        <v>0.1361</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8112</v>
+        <v>-4.9335</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7268</v>
+        <v>-2.1628</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.0844</v>
+        <v>-2.7707</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.1426</v>
+        <v>-3.1418</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9782999999999999</v>
+        <v>-0.982</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.1644</v>
+        <v>-2.1597</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3738</v>
+        <v>-1.3949</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.662</v>
+        <v>-0.6797</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.7689</v>
+        <v>-1.7469</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8934</v>
+        <v>-0.021</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5383</v>
+        <v>0.0531</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3551</v>
+        <v>-0.0741</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5198</v>
+        <v>-3.1547</v>
       </c>
       <c r="E25" t="n">
-        <v>6.122699999999999</v>
+        <v>5.846899999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.6426</v>
+        <v>-9.0016</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3065999999999987</v>
+        <v>-0.2683999999999997</v>
       </c>
       <c r="H25" t="n">
-        <v>7.943000000000001</v>
+        <v>7.968699999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-8.249600000000001</v>
+        <v>-8.2369</v>
       </c>
       <c r="J25" t="n">
-        <v>6.4141</v>
+        <v>6.2256</v>
       </c>
       <c r="K25" t="n">
-        <v>7.014699999999999</v>
+        <v>6.8994</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6002999999999998</v>
+        <v>-0.6735999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-6.7211</v>
+        <v>-6.494</v>
       </c>
       <c r="N25" t="n">
-        <v>0.9285000000000001</v>
+        <v>1.0694</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.6493</v>
+        <v>-7.563400000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-7.939000000000001</v>
+        <v>-7.967</v>
       </c>
       <c r="Q25" t="n">
-        <v>-13.6099</v>
+        <v>-13.6579</v>
       </c>
       <c r="R25" t="n">
-        <v>5.670999999999999</v>
+        <v>5.691</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6049999999999998</v>
+        <v>2.9734</v>
       </c>
       <c r="T25" t="n">
-        <v>0.5598000000000001</v>
+        <v>0.5776</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0452999999999999</v>
+        <v>2.3956</v>
       </c>
       <c r="V25" t="n">
-        <v>2.121</v>
+        <v>2.1075</v>
       </c>
       <c r="W25" t="n">
-        <v>12.7588</v>
+        <v>12.7016</v>
       </c>
       <c r="X25" t="n">
-        <v>-10.6377</v>
+        <v>-10.5941</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104619_W18.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104619_W18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-4.9026</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-12.7014</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104619_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-10.5941</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
